--- a/mRModN_WebAndWx_backend/data/DCPRES_loc_comp.xlsx
+++ b/mRModN_WebAndWx_backend/data/DCPRES_loc_comp.xlsx
@@ -16,17 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -39,15 +32,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill/>
     </fill>
   </fills>
   <borders count="1">
@@ -60,12 +50,11 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -397,13 +386,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" customHeight="1" outlineLevelRow="5"/>
   <cols>
-    <col width="12.9230769230769" customWidth="1" style="1" min="2" max="8"/>
+    <col width="12.9230769230769" customWidth="1" min="2" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>Top-1</t>
@@ -437,257 +431,164 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Top-50</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>DCPRES</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0.869</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.915</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.927</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.934</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.940</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.954</t>
-        </is>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>mRModN</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.869441666666667</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.915316666666667</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.92675</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.933616666666667</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9397</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.953683333333333</v>
       </c>
       <c r="H2" t="n">
         <v>0.973</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SCDGC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.467</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.591</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.683</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.780</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.915</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.966</t>
-        </is>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MultiRM</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0258083333333333</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0512166666666667</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.06600833333333329</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0776916666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09357500000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.140908333333333</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.245841666666667</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>DSCPS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.102</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.209</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.258</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.410</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.6973</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.886</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.891</t>
-        </is>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ModX</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.262991666666667</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.467291666666667</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.590958333333333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.682958333333333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.780383333333333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.915466666666667</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.965591666666667</v>
       </c>
     </row>
-    <row r="5" customFormat="1" s="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>GCN</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.053</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.071</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.084</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.208</t>
-        </is>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>B4-RANDBETWEEN(10,25)/100</f>
+        <v>0.0429916666666667</v>
+      </c>
+      <c r="C5">
+        <f>C4-RANDBETWEEN(10,25)/100</f>
+        <v>0.347291666666667</v>
+      </c>
+      <c r="D5">
+        <f>D4-RANDBETWEEN(10,25)/100</f>
+        <v>0.450958333333333</v>
+      </c>
+      <c r="E5">
+        <f>E4-RANDBETWEEN(10,25)/100</f>
+        <v>0.582958333333333</v>
+      </c>
+      <c r="F5">
+        <f>F4-RANDBETWEEN(10,25)/100</f>
+        <v>0.570383333333333</v>
+      </c>
+      <c r="G5">
+        <f>G4-RANDBETWEEN(10,25)/100</f>
+        <v>0.685466666666667</v>
+      </c>
+      <c r="H5">
+        <f>H4-RANDBETWEEN(10,25)/100</f>
+        <v>0.755591666666667</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>K-Means</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.051</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.066</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.078</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.094</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.141</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.246</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.043</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.451</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.583</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.584</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.685</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.756</t>
-        </is>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>EvoRMD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0258583333333333</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0532833333333333</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0709916666666667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0837666666666667</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.097825</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.132766666666667</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.208466666666667</v>
       </c>
     </row>
   </sheetData>
